--- a/Framework_MWC_Testing/testdata_generation/output/register_2026-05-09_11-22-28/step1.xlsx
+++ b/Framework_MWC_Testing/testdata_generation/output/register_2026-05-09_11-22-28/step1.xlsx
@@ -1,23 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\ThuTrang\Framework_MWC_Testing\testdata_generation\output\register_2026-05-09_11-22-28\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18200" windowHeight="8510" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Bang_EP_BVA" sheetId="2" r:id="rId2"/>
-    <sheet name="Username" sheetId="3" r:id="rId3"/>
-    <sheet name="Phone" sheetId="4" r:id="rId4"/>
-    <sheet name="Password" sheetId="5" r:id="rId5"/>
-    <sheet name="ConfirmPassword" sheetId="6" r:id="rId6"/>
+    <sheet r:id="rId1" sheetId="1" name="Summary"/>
+    <sheet r:id="rId2" sheetId="2" name="Bang_EP_BVA"/>
+    <sheet r:id="rId3" sheetId="3" name="Username"/>
+    <sheet r:id="rId4" sheetId="4" name="Phone"/>
+    <sheet r:id="rId5" sheetId="5" name="Password"/>
+    <sheet r:id="rId6" sheetId="6" name="ConfirmPassword"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">Bang_EP_BVA!$A$6:$H$29</definedName>
@@ -27,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$11:$E$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">Username!$A$9:$L$12</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -541,7 +536,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -552,7 +548,7 @@
     </font>
     <font>
       <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFffffff"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -564,13 +560,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFffffff"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -584,17 +580,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
+        <fgColor rgb="FF1f4e78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAF7"/>
+        <fgColor rgb="FFd9eaf7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC99700"/>
+        <fgColor rgb="FFc99700"/>
       </patternFill>
     </fill>
   </fills>
@@ -608,31 +604,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </left>
       <right style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </right>
       <top style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFC6C6C6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="FFc6c6c6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,111 +624,108 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFd9d9d9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFd9d9d9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFd9d9d9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFd9d9d9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="25">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -758,10 +736,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -799,71 +777,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -891,7 +869,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -914,11 +892,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -927,13 +905,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -943,7 +921,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -952,7 +930,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -961,7 +939,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -969,10 +947,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1042,228 +1020,229 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" style="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.54296875" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="21" width="36.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="45.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="14" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="21" width="17.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="25"/>
-    </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="15"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="18"/>
-    </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="22"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="16"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="22"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="18"/>
-    </row>
-    <row r="4" spans="1:6" ht="84.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="22"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="84.5">
+      <c r="A4" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="18"/>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="22"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="6">
         <v>14</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="18"/>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="22"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="6">
         <v>9</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="18"/>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="22"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="6">
         <v>23</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="18"/>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="22"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="6">
         <v>4</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="18"/>
-    </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="15"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="18"/>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="15"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="18"/>
-    </row>
-    <row r="11" spans="1:6" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="22"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="16"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="22"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="16"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="22"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="8">
+      <c r="A11" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="F11" s="20"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="16" t="s">
+      <c r="F11" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>23</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <v>14</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="7">
         <v>9</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="F12" s="18"/>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="16" t="s">
+      <c r="F12" s="22"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="7">
         <v>3</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="7">
         <v>3</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="7">
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F13" s="18"/>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="16" t="s">
+      <c r="F13" s="22"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="7">
         <v>9</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
         <v>6</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="7">
         <v>3</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="18"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="16" t="s">
+      <c r="F14" s="22"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="7">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="7">
         <v>2</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="7">
         <v>6</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="18"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="16" t="s">
+      <c r="F15" s="22"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <v>3</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="7">
         <v>3</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="7">
         <v>0</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F16" s="18"/>
+      <c r="F16" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1279,659 +1258,659 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.54296875" style="14" customWidth="1"/>
-    <col min="4" max="4" width="14" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.453125" style="14" customWidth="1"/>
-    <col min="6" max="6" width="28" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="13" width="12.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="21" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="33.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="13" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="25.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="15" width="28.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="13" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="13" width="12.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-    </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="28" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="4"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-    </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="29" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="4"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="8">
+      <c r="A5" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="30"/>
-      <c r="E5" s="29" t="s">
+      <c r="D5" s="19"/>
+      <c r="E5" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="18" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="30"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="8" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="8">
+      <c r="A6" s="19"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-    </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="10" t="s">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11" t="s">
+      <c r="D7" s="11"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="11" t="s">
+      <c r="D8" s="11"/>
+      <c r="E8" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="A9" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="11" t="s">
+      <c r="D9" s="11"/>
+      <c r="E9" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11" t="s">
+      <c r="D10" s="11"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="11" t="s">
+      <c r="D11" s="11"/>
+      <c r="E11" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="33">
+      <c r="A12" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="33">
+      <c r="A17" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="11" t="s">
+      <c r="D18" s="11"/>
+      <c r="E18" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+      <c r="A19" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="11" t="s">
+      <c r="D19" s="11"/>
+      <c r="E19" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+      <c r="A20" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11" t="s">
+      <c r="D20" s="11"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="11" t="s">
+      <c r="D21" s="11"/>
+      <c r="E21" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="11" t="s">
+      <c r="D22" s="11"/>
+      <c r="E22" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="36">
+      <c r="A23" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="11" t="s">
+      <c r="D23" s="11"/>
+      <c r="E23" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11" t="s">
+      <c r="D27" s="11"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="G27" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="11" t="s">
+      <c r="D28" s="11"/>
+      <c r="E28" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="G28" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="39">
+      <c r="A29" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="11" t="s">
+      <c r="D29" s="11"/>
+      <c r="E29" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="11" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1957,287 +1936,287 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="13" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="38.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="15" width="24.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="30.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="13" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="15" width="32.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="13" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="24.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="13" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="13" width="22.005" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="13" width="24.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-    </row>
-    <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="4"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>0</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>3</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="4"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="8">
+      <c r="A9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>1</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11" t="s">
+      <c r="D10" s="12"/>
+      <c r="E10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-    </row>
-    <row r="11" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="10" t="s">
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>2</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-    </row>
-    <row r="12" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="10" t="s">
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>3</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2253,489 +2232,489 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="13" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="38.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="15" width="24.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="30.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="13" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="15" width="32.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="13" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="24.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="13" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="13" width="22.005" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="13" width="24.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-    </row>
-    <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="4"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>6</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>3</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>9</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="4"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="8">
+      <c r="A9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>7</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-    </row>
-    <row r="11" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="10" t="s">
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>8</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-    </row>
-    <row r="12" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="10" t="s">
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>9</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-    </row>
-    <row r="13" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="10" t="s">
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="7">
         <v>10</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-    </row>
-    <row r="14" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="10" t="s">
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="7">
         <v>11</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-    </row>
-    <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="7">
         <v>23</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11" t="s">
+      <c r="D15" s="12"/>
+      <c r="E15" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-    </row>
-    <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="10" t="s">
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <v>4</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10" t="s">
+      <c r="I16" s="11"/>
+      <c r="J16" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L16" s="10" t="s">
+      <c r="L16" s="11" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="7">
         <v>5</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10" t="s">
+      <c r="I17" s="11"/>
+      <c r="J17" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L17" s="10" t="s">
+      <c r="L17" s="11" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="7">
         <v>6</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10" t="s">
+      <c r="I18" s="11"/>
+      <c r="J18" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="K18" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L18" s="10" t="s">
+      <c r="L18" s="11" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2753,469 +2732,469 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="13" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="38.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="15" width="24.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="30.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="13" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="15" width="32.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="13" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="24.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="13" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="13" width="22.005" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="13" width="24.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-    </row>
-    <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="4"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>2</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>6</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>8</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="4"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="8">
+      <c r="A9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>18</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11" t="s">
+      <c r="D10" s="12"/>
+      <c r="E10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-    </row>
-    <row r="11" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="10" t="s">
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>19</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-    </row>
-    <row r="12" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="10" t="s">
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>12</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10" t="s">
+      <c r="I12" s="11"/>
+      <c r="J12" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="L12" s="11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="7">
         <v>13</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10" t="s">
+      <c r="I13" s="11"/>
+      <c r="J13" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="L13" s="11" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="7">
         <v>14</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10" t="s">
+      <c r="I14" s="11"/>
+      <c r="J14" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="K14" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="L14" s="10" t="s">
+      <c r="L14" s="11" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="7">
         <v>15</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10" t="s">
+      <c r="I15" s="11"/>
+      <c r="J15" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="L15" s="10" t="s">
+      <c r="L15" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <v>16</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10" t="s">
+      <c r="I16" s="11"/>
+      <c r="J16" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="L16" s="10" t="s">
+      <c r="L16" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="7">
         <v>17</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10" t="s">
+      <c r="I17" s="11"/>
+      <c r="J17" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="L17" s="10" t="s">
+      <c r="L17" s="11" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3233,287 +3212,287 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="13" width="10.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="14.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="38.005" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="15" width="24.005" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="30.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="13" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="15" width="32.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="13" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="24.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="13" width="16.005" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="13" width="22.005" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="13" width="24.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="22" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-    </row>
-    <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="4"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>0</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>3</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" s="7" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="4"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="8">
+      <c r="A9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="10" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>20</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11" t="s">
+      <c r="D10" s="12"/>
+      <c r="E10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-    </row>
-    <row r="11" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="10" t="s">
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>21</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-    </row>
-    <row r="12" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="10" t="s">
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>22</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Framework_MWC_Testing/testdata_generation/output/register_2026-05-09_11-22-28/step1.xlsx
+++ b/Framework_MWC_Testing/testdata_generation/output/register_2026-05-09_11-22-28/step1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Summary"/>
@@ -12,24 +12,24 @@
     <sheet r:id="rId3" sheetId="3" name="Username"/>
     <sheet r:id="rId4" sheetId="4" name="Phone"/>
     <sheet r:id="rId5" sheetId="5" name="Password"/>
-    <sheet r:id="rId6" sheetId="6" name="ConfirmPassword"/>
+    <sheet r:id="rId6" sheetId="6" name="PasswordConfirm"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">Bang_EP_BVA!$A$6:$H$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5">ConfirmPassword!$A$9:$L$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4">Password!$A$9:$L$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3">Phone!$A$9:$L$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Summary!$A$11:$E$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Username!$A$9:$L$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Summary'!$A$11:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Bang_EP_BVA'!$A$6:$H$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Username'!$A$9:$L$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3">'Phone'!$A$9:$L$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Password'!$A$9:$L$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5">'PasswordConfirm'!$A$9:$L$12</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="168">
-  <si>
-    <t>STEP 1 - REGISTER - ConfirmPassword</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="168">
+  <si>
+    <t>STEP 1 - REGISTER - PasswordConfirm</t>
   </si>
   <si>
     <t>Feature</t>
@@ -41,7 +41,7 @@
     <t>Field</t>
   </si>
   <si>
-    <t>ConfirmPassword</t>
+    <t>PasswordConfirm</t>
   </si>
   <si>
     <t>EP Items</t>
@@ -92,7 +92,7 @@
     <t>C1</t>
   </si>
   <si>
-    <t>ConfirmPassword rỗng</t>
+    <t>PasswordConfirm rỗng</t>
   </si>
   <si>
     <t>Vui lòng điền vào trường này</t>
@@ -110,13 +110,13 @@
     <t>C2</t>
   </si>
   <si>
-    <t>ConfirmPassword không khớp với Password</t>
+    <t>PasswordConfirm không khớp với Password</t>
   </si>
   <si>
     <t>Pass12345678901</t>
   </si>
   <si>
-    <t>Số điện thoại không hợp lệ</t>
+    <t>mật khẩu không giống nhau</t>
   </si>
   <si>
     <t>Phải khớp với Password</t>
@@ -125,7 +125,7 @@
     <t>C3</t>
   </si>
   <si>
-    <t>ConfirmPassword khớp với Password</t>
+    <t>PasswordConfirm khớp với Password</t>
   </si>
   <si>
     <t>Pass1234567890</t>
@@ -155,7 +155,7 @@
     <t>Pass123</t>
   </si>
   <si>
-    <t>Mật khẩu phải từ 8 đến 20 ký tự</t>
+    <t>Mật khẩu phải lớn hơn 8 ký tự và nhỏ hơn 20 ký tự!</t>
   </si>
   <si>
     <t>BVA</t>
@@ -248,13 +248,16 @@
     <t>1234567890</t>
   </si>
   <si>
+    <t>Số điện thoại không đúng định dạng!</t>
+  </si>
+  <si>
     <t>Bắt buộc bắt đầu bằng số 0</t>
   </si>
   <si>
     <t>Phone chứa ký tự chữ</t>
   </si>
   <si>
-    <t>01234a6789</t>
+    <t>03234a6789</t>
   </si>
   <si>
     <t>Chỉ được chứa ký tự số (0-9)</t>
@@ -263,7 +266,7 @@
     <t>Phone chứa ký tự đặc biệt</t>
   </si>
   <si>
-    <t>01234!6789</t>
+    <t>03234!6789</t>
   </si>
   <si>
     <t>Không được chứa ký tự đặc biệt (!@#$%^&amp;*)</t>
@@ -272,7 +275,7 @@
     <t>Phone chứa khoảng trắng</t>
   </si>
   <si>
-    <t>01234 6789</t>
+    <t>03234 6789</t>
   </si>
   <si>
     <t>Không được chứa khoảng trắng</t>
@@ -281,7 +284,7 @@
     <t>Phone hợp lệ</t>
   </si>
   <si>
-    <t>0123456789</t>
+    <t>0323456789</t>
   </si>
   <si>
     <t>Phone rỗng</t>
@@ -290,7 +293,7 @@
     <t>Phone có độ dài 9 ký tự</t>
   </si>
   <si>
-    <t>012345678</t>
+    <t>032345678</t>
   </si>
   <si>
     <t>Đúng 10 ký tự</t>
@@ -317,7 +320,7 @@
     <t>Phone có độ dài 11 ký tự</t>
   </si>
   <si>
-    <t>01234567890</t>
+    <t>03234567890</t>
   </si>
   <si>
     <t>N+1</t>
@@ -353,9 +356,6 @@
     <t>BẢNG EP + BVA - REGISTER</t>
   </si>
   <si>
-    <t>Bảng này trình bày Step 1 theo dạng gần giống mẫu bài giảng.</t>
-  </si>
-  <si>
     <t>Test case</t>
   </si>
   <si>
@@ -374,70 +374,70 @@
     <t>TC1</t>
   </si>
   <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>TC2</t>
   </si>
   <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>TC3</t>
+  </si>
+  <si>
+    <t>Không hợp lệ</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>TC4</t>
+  </si>
+  <si>
+    <t>Hợp lệ</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>TC5</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>TC6</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>TC7</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>TC8</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>TC9</t>
+  </si>
+  <si>
+    <t>TC10</t>
+  </si>
+  <si>
     <t>21</t>
   </si>
   <si>
-    <t>TC3</t>
+    <t>TC11</t>
   </si>
   <si>
     <t>22</t>
-  </si>
-  <si>
-    <t>TC4</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>TC5</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>TC6</t>
-  </si>
-  <si>
-    <t>Không hợp lệ</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>TC7</t>
-  </si>
-  <si>
-    <t>Hợp lệ</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>TC8</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>TC9</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>TC10</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>TC11</t>
-  </si>
-  <si>
-    <t>17</t>
   </si>
   <si>
     <t>TC12</t>
@@ -538,7 +538,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -549,12 +549,6 @@
     <font>
       <sz val="14"/>
       <color rgb="FFffffff"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -643,7 +637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -657,28 +651,28 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -693,29 +687,20 @@
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="4" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1022,12 +1007,12 @@
   <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="21" width="36.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="20" width="36.005" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="14" width="45.005" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="14" width="12.005" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="14" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="21" width="17.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="24" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="20" width="17.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -1038,7 +1023,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="16"/>
-      <c r="F1" s="22"/>
+      <c r="F1" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="16"/>
@@ -1046,7 +1031,7 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="16"/>
-      <c r="F2" s="22"/>
+      <c r="F2" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="5" t="s">
@@ -1058,19 +1043,19 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="16"/>
-      <c r="F3" s="22"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="84.5">
+      <c r="F3" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="21" t="s">
         <v>161</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="16"/>
-      <c r="F4" s="22"/>
+      <c r="F4" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="5" t="s">
@@ -1082,7 +1067,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="16"/>
-      <c r="F5" s="22"/>
+      <c r="F5" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="5" t="s">
@@ -1094,7 +1079,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="16"/>
-      <c r="F6" s="22"/>
+      <c r="F6" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="5" t="s">
@@ -1106,7 +1091,7 @@
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="16"/>
-      <c r="F7" s="22"/>
+      <c r="F7" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="5" t="s">
@@ -1118,7 +1103,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="16"/>
-      <c r="F8" s="22"/>
+      <c r="F8" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="16"/>
@@ -1126,7 +1111,7 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="22"/>
+      <c r="F9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="16"/>
@@ -1134,7 +1119,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="16"/>
-      <c r="F10" s="22"/>
+      <c r="F10" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="8">
       <c r="A11" s="9" t="s">
@@ -1155,7 +1140,7 @@
       <c r="F11" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="19" t="s">
         <v>166</v>
       </c>
       <c r="B12" s="7">
@@ -1167,14 +1152,14 @@
       <c r="D12" s="7">
         <v>9</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="F12" s="22"/>
+      <c r="F12" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="20" t="s">
-        <v>99</v>
+      <c r="A13" s="19" t="s">
+        <v>100</v>
       </c>
       <c r="B13" s="7">
         <v>3</v>
@@ -1185,13 +1170,13 @@
       <c r="D13" s="7">
         <v>0</v>
       </c>
-      <c r="E13" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="F13" s="22"/>
+      <c r="E13" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="19" t="s">
         <v>70</v>
       </c>
       <c r="B14" s="7">
@@ -1203,13 +1188,13 @@
       <c r="D14" s="7">
         <v>3</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="22"/>
+      <c r="F14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="19" t="s">
         <v>37</v>
       </c>
       <c r="B15" s="7">
@@ -1221,13 +1206,13 @@
       <c r="D15" s="7">
         <v>6</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="22"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="20" t="s">
+      <c r="F15" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="19" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="7">
@@ -1239,10 +1224,10 @@
       <c r="D16" s="7">
         <v>0</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F16" s="22"/>
+      <c r="F16" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1261,10 +1246,10 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="13" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="21" width="18.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="15" width="33.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="20" width="18.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="28.005" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="13" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="15" width="25.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="20.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="15" width="28.005" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="13" width="14.005" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="13" width="12.005" customWidth="1" bestFit="1"/>
@@ -1272,7 +1257,7 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="3"/>
@@ -1293,9 +1278,7 @@
       <c r="H2" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="17" t="s">
-        <v>108</v>
-      </c>
+      <c r="A3" s="4"/>
       <c r="B3" s="16"/>
       <c r="C3" s="3"/>
       <c r="D3" s="4"/>
@@ -1315,31 +1298,31 @@
       <c r="H4" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="8">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="18" t="s">
+      <c r="D5" s="18"/>
+      <c r="E5" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="17" t="s">
         <v>113</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="8">
-      <c r="A6" s="19"/>
+      <c r="A6" s="18"/>
       <c r="B6" s="3"/>
       <c r="C6" s="9" t="s">
         <v>23</v>
@@ -1349,15 +1332,15 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>4</v>
+      <c r="B7" s="19" t="s">
+        <v>37</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>24</v>
@@ -1368,7 +1351,7 @@
         <v>22</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>59</v>
+        <v>115</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>23</v>
@@ -1376,171 +1359,179 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>4</v>
+        <v>116</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>37</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="12" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="33">
       <c r="A9" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>4</v>
+        <v>118</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>37</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="11"/>
+        <v>119</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="E9" s="12" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="19" t="s">
         <v>37</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="12"/>
+        <v>122</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>50</v>
+      </c>
       <c r="F10" s="12" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B11" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="19" t="s">
         <v>37</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="11"/>
+        <v>122</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>55</v>
+      </c>
       <c r="E11" s="12" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="33">
       <c r="A12" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="B12" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="19" t="s">
         <v>37</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="33">
       <c r="A13" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="19" t="s">
         <v>37</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="33">
       <c r="A14" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>37</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>43</v>
@@ -1548,98 +1539,90 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>37</v>
+        <v>132</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>4</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>58</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="12"/>
       <c r="F15" s="12" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="B16" s="20" t="s">
-        <v>37</v>
+      <c r="B16" s="19" t="s">
+        <v>4</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>64</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D16" s="11"/>
       <c r="E16" s="12" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G16" s="11" t="s">
         <v>134</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="33">
+        <v>23</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B17" s="20" t="s">
-        <v>37</v>
+      <c r="B17" s="19" t="s">
+        <v>4</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>68</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D17" s="11"/>
       <c r="E17" s="12" t="s">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>136</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+        <v>23</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="33">
       <c r="A18" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="19" t="s">
         <v>70</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="12" t="s">
         <v>72</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>138</v>
@@ -1652,7 +1635,7 @@
       <c r="A19" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="19" t="s">
         <v>70</v>
       </c>
       <c r="C19" s="12" t="s">
@@ -1660,7 +1643,7 @@
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>34</v>
@@ -1676,7 +1659,7 @@
       <c r="A20" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="19" t="s">
         <v>70</v>
       </c>
       <c r="C20" s="12" t="s">
@@ -1694,22 +1677,22 @@
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="33">
       <c r="A21" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="19" t="s">
         <v>70</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>46</v>
@@ -1718,46 +1701,46 @@
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="33">
       <c r="A22" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="19" t="s">
         <v>70</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="36">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="33">
       <c r="A23" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="19" t="s">
         <v>70</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D23" s="11"/>
       <c r="E23" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>146</v>
@@ -1766,24 +1749,24 @@
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="33">
       <c r="A24" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="19" t="s">
         <v>70</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>148</v>
@@ -1792,21 +1775,21 @@
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="19" t="s">
         <v>70</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>34</v>
@@ -1822,20 +1805,20 @@
       <c r="A26" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="19" t="s">
         <v>70</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D26" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E26" s="12" t="s">
-        <v>96</v>
-      </c>
       <c r="F26" s="12" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>152</v>
@@ -1848,8 +1831,8 @@
       <c r="A27" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B27" s="20" t="s">
-        <v>99</v>
+      <c r="B27" s="19" t="s">
+        <v>100</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>24</v>
@@ -1870,15 +1853,15 @@
       <c r="A28" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="B28" s="20" t="s">
-        <v>99</v>
+      <c r="B28" s="19" t="s">
+        <v>100</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>24</v>
       </c>
       <c r="D28" s="11"/>
       <c r="E28" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>34</v>
@@ -1890,22 +1873,22 @@
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="39">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B29" s="20" t="s">
-        <v>99</v>
+      <c r="B29" s="19" t="s">
+        <v>100</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>158</v>
@@ -1915,9 +1898,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:D5"/>
@@ -1954,7 +1936,7 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -2005,7 +1987,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -2132,7 +2114,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="12" t="s">
@@ -2162,19 +2144,19 @@
         <v>2</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>25</v>
@@ -2194,10 +2176,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>34</v>
@@ -2420,7 +2402,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="33">
       <c r="A10" s="11" t="s">
         <v>20</v>
       </c>
@@ -2434,13 +2416,13 @@
         <v>72</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>25</v>
@@ -2452,7 +2434,7 @@
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="33">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2460,19 +2442,19 @@
         <v>8</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>25</v>
@@ -2484,7 +2466,7 @@
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="33">
       <c r="A12" s="11" t="s">
         <v>31</v>
       </c>
@@ -2492,19 +2474,19 @@
         <v>9</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>25</v>
@@ -2516,7 +2498,7 @@
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="33">
       <c r="A13" s="11" t="s">
         <v>48</v>
       </c>
@@ -2524,19 +2506,19 @@
         <v>10</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>25</v>
@@ -2548,7 +2530,7 @@
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="11" t="s">
         <v>52</v>
       </c>
@@ -2556,10 +2538,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>34</v>
@@ -2580,7 +2562,7 @@
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="11" t="s">
         <v>56</v>
       </c>
@@ -2588,7 +2570,7 @@
         <v>23</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="12" t="s">
@@ -2610,7 +2592,7 @@
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="33">
       <c r="A16" s="11" t="s">
         <v>61</v>
       </c>
@@ -2618,35 +2600,35 @@
         <v>4</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>43</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>25</v>
       </c>
       <c r="I16" s="11"/>
       <c r="J16" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+        <v>92</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="11" t="s">
         <v>65</v>
       </c>
@@ -2654,10 +2636,10 @@
         <v>5</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>34</v>
@@ -2666,56 +2648,56 @@
         <v>43</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H17" s="11" t="s">
         <v>35</v>
       </c>
       <c r="I17" s="11"/>
       <c r="J17" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+        <v>94</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="33.75">
       <c r="A18" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B18" s="7">
         <v>6</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>43</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>25</v>
       </c>
       <c r="I18" s="11"/>
       <c r="J18" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3400,7 +3382,7 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="11" t="s">
         <v>20</v>
       </c>
@@ -3430,7 +3412,7 @@
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="33">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -3462,7 +3444,7 @@
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="20.25">
       <c r="A12" s="11" t="s">
         <v>31</v>
       </c>
